--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusiInfoRegistAll.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusiInfoRegistAll.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="223">
   <si>
     <t>2.必填要素请参照《数据元规范》。</t>
   </si>
@@ -786,6 +786,18 @@
   </si>
   <si>
     <t xml:space="preserve">  数据状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  交易序列号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  关联活期存款账号开户行代码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  关联活期存款账号开户行名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1011,11 +1023,17 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1303,16 +1321,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG2"/>
+  <dimension ref="A1:AJ2"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5546875" style="16" customWidth="1" collapsed="1"/>
     <col min="2" max="14" width="25.5546875" style="16" customWidth="1" collapsed="1"/>
     <col min="15" max="15" width="25.5546875" style="17" customWidth="1" collapsed="1"/>
-    <col min="16" max="33" width="25.5546875" style="17" customWidth="1"/>
+    <col min="16" max="26" width="25.5546875" style="17" customWidth="1"/>
+    <col min="27" max="27" width="33" style="17" customWidth="1"/>
+    <col min="28" max="28" width="32.21875" style="17" customWidth="1"/>
+    <col min="29" max="36" width="25.5546875" style="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>219</v>
       </c>
@@ -1386,34 +1407,43 @@
         <v>209</v>
       </c>
       <c r="Y1" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="Z1" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="Z1" s="11" t="s">
+      <c r="AA1" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB1" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="AC1" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="AA1" s="11" t="s">
+      <c r="AD1" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="AB1" s="11" t="s">
+      <c r="AE1" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="AC1" s="11" t="s">
+      <c r="AF1" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="AD1" s="11" t="s">
+      <c r="AG1" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="AE1" s="11" t="s">
+      <c r="AH1" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="AF1" s="11" t="s">
+      <c r="AI1" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="AG1" s="11" t="s">
+      <c r="AJ1" s="11" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="2" spans="1:33" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18"/>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -1447,6 +1477,9 @@
       <c r="AE2" s="19"/>
       <c r="AF2" s="19"/>
       <c r="AG2" s="19"/>
+      <c r="AH2" s="19"/>
+      <c r="AI2" s="19"/>
+      <c r="AJ2" s="19"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
